--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№1.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="430" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -191,18 +191,18 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="true"/>
-    <col min="2" max="2" width="15.85546875" customWidth="true"/>
-    <col min="3" max="3" width="15.85546875" customWidth="true"/>
-    <col min="4" max="4" width="15.85546875" customWidth="true"/>
+    <col min="2" max="2" width="14.85546875" customWidth="true"/>
+    <col min="3" max="3" width="11.42578125" customWidth="true"/>
+    <col min="4" max="4" width="14.85546875" customWidth="true"/>
     <col min="5" max="5" width="12.85546875" customWidth="true"/>
-    <col min="6" max="6" width="15.85546875" customWidth="true"/>
-    <col min="7" max="7" width="15.85546875" customWidth="true"/>
-    <col min="8" max="8" width="15.85546875" customWidth="true"/>
-    <col min="9" max="9" width="15.85546875" customWidth="true"/>
-    <col min="10" max="10" width="15.85546875" customWidth="true"/>
-    <col min="11" max="11" width="15.85546875" customWidth="true"/>
-    <col min="12" max="12" width="15.85546875" customWidth="true"/>
-    <col min="13" max="13" width="15.85546875" customWidth="true"/>
+    <col min="6" max="6" width="11.140625" customWidth="true"/>
+    <col min="7" max="7" width="14.85546875" customWidth="true"/>
+    <col min="8" max="8" width="12.85546875" customWidth="true"/>
+    <col min="9" max="9" width="11.140625" customWidth="true"/>
+    <col min="10" max="10" width="11.140625" customWidth="true"/>
+    <col min="11" max="11" width="13.85546875" customWidth="true"/>
+    <col min="12" max="12" width="13.85546875" customWidth="true"/>
+    <col min="13" max="13" width="11.140625" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>39309616874265656</v>
+        <v>537369626</v>
       </c>
       <c r="C2" s="0">
-        <v>38465223895260384</v>
+        <v>537391760</v>
       </c>
       <c r="D2" s="0">
-        <v>6.0093335284299768e+19</v>
+        <v>1074783520</v>
       </c>
       <c r="E2" s="0">
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>1.4306992026882105e+19</v>
+        <v>1074522352</v>
       </c>
       <c r="G2" s="0">
-        <v>3.7217846238007167e+22</v>
+        <v>2147203448</v>
       </c>
       <c r="H2" s="0">
-        <v>2.526336788612916e+22</v>
+        <v>2146925120</v>
       </c>
       <c r="I2" s="0">
-        <v>5.6117497474289238e+21</v>
+        <v>2678332088</v>
       </c>
       <c r="J2" s="0">
-        <v>1.1792398619062411e+25</v>
+        <v>4294406896</v>
       </c>
       <c r="K2" s="0">
-        <v>1.1099100309604073e+25</v>
+        <v>5636252321</v>
       </c>
       <c r="L2" s="0">
-        <v>1.1329520188131308e+25</v>
+        <v>5636252321</v>
       </c>
       <c r="M2" s="0">
-        <v>2.6832171746965584e+24</v>
+        <v>6964681208</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>39328820399851520</v>
+        <v>537391760</v>
       </c>
       <c r="C3" s="0">
-        <v>30763667107612424</v>
+        <v>537286571</v>
       </c>
       <c r="D3" s="0">
-        <v>6.0093335284299768e+19</v>
+        <v>1074331184</v>
       </c>
       <c r="E3" s="0">
         <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>1.4415684563371868e+19</v>
+        <v>1074493146</v>
       </c>
       <c r="G3" s="0">
-        <v>2.3334118073838179e+22</v>
+        <v>1074739252</v>
       </c>
       <c r="H3" s="0">
-        <v>3.3161019366045982e+22</v>
+        <v>2148319959</v>
       </c>
       <c r="I3" s="0">
-        <v>5.6920467355436948e+21</v>
+        <v>2675344297</v>
       </c>
       <c r="J3" s="0">
-        <v>1.3170838711966101e+25</v>
+        <v>2147240664</v>
       </c>
       <c r="K3" s="0">
-        <v>1.086784876209644e+25</v>
+        <v>4561310032</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>39309616874265656</v>
+        <v>537369626</v>
       </c>
       <c r="C4" s="0">
-        <v>38359792668526832</v>
+        <v>537268807</v>
       </c>
       <c r="D4" s="0">
-        <v>6.0093335284299768e+19</v>
+        <v>1074331184</v>
       </c>
       <c r="E4" s="0">
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>1.4415684563371868e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="G4" s="0">
-        <v>2.4853784006849796e+22</v>
+        <v>1612437132</v>
       </c>
       <c r="H4" s="0">
-        <v>2.3958038863996705e+22</v>
+        <v>2146925120</v>
       </c>
       <c r="I4" s="0">
-        <v>5.6920467355436948e+21</v>
+        <v>2147250176</v>
       </c>
       <c r="J4" s="0">
-        <v>8.7264476377700687e+24</v>
+        <v>2147652520</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>38454648946634752</v>
+        <v>537171140</v>
       </c>
       <c r="C5" s="0">
-        <v>21742033298164892</v>
+        <v>537357153</v>
       </c>
       <c r="D5" s="0">
-        <v>6.1882906405721874e+19</v>
+        <v>1073877548</v>
       </c>
       <c r="E5" s="0">
         <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>1.348392977000706e+19</v>
+        <v>1074522352</v>
       </c>
       <c r="G5" s="0">
-        <v>3.2146880044333141e+22</v>
+        <v>2148757560</v>
       </c>
       <c r="H5" s="0">
-        <v>3.3161019366045982e+22</v>
+        <v>1610438580</v>
       </c>
       <c r="I5" s="0">
-        <v>4.7848286442266307e+21</v>
+        <v>2679446389</v>
       </c>
       <c r="J5" s="0">
-        <v>1.231627147219316e+25</v>
+        <v>2686519876</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>39309616874265656</v>
+        <v>537369626</v>
       </c>
       <c r="C6" s="0">
-        <v>38465223895260384</v>
+        <v>537391760</v>
       </c>
       <c r="D6" s="0">
-        <v>6.1448832875543601e+19</v>
+        <v>1074342280</v>
       </c>
       <c r="E6" s="0">
         <v>0</v>
       </c>
       <c r="F6" s="0">
-        <v>1.4306992026882105e+19</v>
+        <v>1074493146</v>
       </c>
       <c r="G6" s="0">
-        <v>3.7217846238007167e+22</v>
+        <v>2147203448</v>
       </c>
       <c r="H6" s="0">
-        <v>2.2893363955117104e+22</v>
+        <v>1342502669</v>
       </c>
       <c r="I6" s="0">
-        <v>5.1343204773776924e+21</v>
+        <v>2679446389</v>
       </c>
       <c r="J6" s="0">
-        <v>1.0294861281604517e+25</v>
+        <v>4297515120</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>38454648946634752</v>
+        <v>537171140</v>
       </c>
       <c r="C7" s="0">
-        <v>38465223895260384</v>
+        <v>537391760</v>
       </c>
       <c r="D7" s="0">
-        <v>6.2155569472071508e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="E7" s="0">
         <v>0</v>
       </c>
       <c r="F7" s="0">
-        <v>1.2079662952393007e+19</v>
+        <v>1074436690</v>
       </c>
       <c r="G7" s="0">
-        <v>2.4807843464398743e+22</v>
+        <v>1074493146</v>
       </c>
       <c r="H7" s="0">
-        <v>2.5863388507724331e+22</v>
+        <v>2147547786</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>39309616874265656</v>
+        <v>537369626</v>
       </c>
       <c r="C8" s="0">
-        <v>38465223895260384</v>
+        <v>537391760</v>
       </c>
       <c r="D8" s="0">
-        <v>6.0051877318816014e+19</v>
+        <v>1073877548</v>
       </c>
       <c r="E8" s="0">
         <v>0</v>
       </c>
       <c r="F8" s="0">
-        <v>1.3796214504960713e+19</v>
+        <v>1074522352</v>
       </c>
       <c r="G8" s="0">
-        <v>2.7341584138654724e+22</v>
+        <v>2148684560</v>
       </c>
       <c r="H8" s="0">
-        <v>2.7172816260276666e+22</v>
+        <v>1611003396</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>38454648946634752</v>
+        <v>537189390</v>
       </c>
       <c r="C9" s="0">
-        <v>38359792668526832</v>
+        <v>537286571</v>
       </c>
       <c r="D9" s="0">
-        <v>6.0051877318816014e+19</v>
+        <v>1074342280</v>
       </c>
       <c r="E9" s="0">
         <v>0</v>
       </c>
       <c r="F9" s="0">
-        <v>1.4415684563371868e+19</v>
+        <v>1074436690</v>
       </c>
       <c r="G9" s="0">
-        <v>2.2260803720995888e+22</v>
+        <v>1610240992</v>
       </c>
       <c r="H9" s="0">
-        <v>3.590891889292804e+22</v>
+        <v>2147121040</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>39328820399851520</v>
+        <v>537391760</v>
       </c>
       <c r="C10" s="0">
-        <v>30763667107612424</v>
+        <v>537357153</v>
       </c>
       <c r="D10" s="0">
-        <v>6.0051877318816014e+19</v>
+        <v>1073371512</v>
       </c>
       <c r="E10" s="0">
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>1.3856489012611834e+19</v>
+        <v>1074436690</v>
       </c>
       <c r="G10" s="0">
-        <v>2.323682077682562e+22</v>
+        <v>1074187829</v>
       </c>
       <c r="H10" s="0">
-        <v>2.7811609226035985e+22</v>
+        <v>2147164536</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>38454648946634752</v>
+        <v>537171140</v>
       </c>
       <c r="C11" s="0">
-        <v>38359792668526832</v>
+        <v>537357153</v>
       </c>
       <c r="D11" s="0">
-        <v>4.4071101495380238e+19</v>
+        <v>1073877548</v>
       </c>
       <c r="E11" s="0">
         <v>0</v>
       </c>
       <c r="F11" s="0">
-        <v>1.3856489012611834e+19</v>
+        <v>1074436690</v>
       </c>
       <c r="G11" s="0">
-        <v>2.5311585707214294e+22</v>
+        <v>1074436690</v>
       </c>
       <c r="H11" s="0">
-        <v>3.590891889292804e+22</v>
+        <v>2147121040</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>39328820399851520</v>
+        <v>537391760</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>4.2694489259287552e+19</v>
+        <v>1074342280</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>2.3311423579011624e+22</v>
+        <v>2148662368</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>36852037222296784</v>
+        <v>537165592</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>4.3123081961729458e+19</v>
+        <v>537206858</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>2.2219301972355632e+22</v>
+        <v>2146743024</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>39328820399851520</v>
+        <v>537391760</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>6.0368347192270905e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>2.6761592873831958e+22</v>
+        <v>1074071774</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>36852037222296784</v>
+        <v>537189390</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>6.1101304178357084e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>2.7341584138654724e+22</v>
+        <v>1074436690</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>38454648946634752</v>
+        <v>537171140</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>6.2155569472071508e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>2.3311423579011624e+22</v>
+        <v>1611842734</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>37702050908699520</v>
+        <v>537189390</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>6.1816493074673508e+19</v>
+        <v>537160395</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>3.7002794329369033e+22</v>
+        <v>2148757560</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>38454648946634752</v>
+        <v>537171140</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>6.1816493074673508e+19</v>
+        <v>1074783520</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>3.2146880044333141e+22</v>
+        <v>2147164536</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>37702050908699520</v>
+        <v>537189390</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>6.1816493074673508e+19</v>
+        <v>1073371512</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>2.2325097321077827e+22</v>
+        <v>1074378780</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>36852037222296784</v>
+        <v>537165592</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>6.0237260298236305e+19</v>
+        <v>537357153</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>2.2219301972355632e+22</v>
+        <v>1611842734</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>36791713582641864</v>
+        <v>537189390</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>6.0237260298236305e+19</v>
+        <v>1074783520</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>3.7002794329369033e+22</v>
+        <v>2148757560</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>6.0237260298236305e+19</v>
+        <v>1074331184</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>6.0368347192270905e+19</v>
+        <v>1073582268</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>6.1882906405721874e+19</v>
+        <v>1073582268</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>6.2155569472071508e+19</v>
+        <v>1074378780</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>6.4045081082448896e+19</v>
+        <v>537525774</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>6.4045081082448896e+19</v>
+        <v>537525774</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>6.4045081082448896e+19</v>
+        <v>1074342280</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>6.0010419353332253e+19</v>
+        <v>1073601724</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>6.0010419353332253e+19</v>
+        <v>1073601724</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>6.0010419353332253e+19</v>
+        <v>1073601724</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>

--- a/src/width_txt/Максимальные_значения_определителя_АЦП_№1.xlsx
+++ b/src/width_txt/Максимальные_значения_определителя_АЦП_№1.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="602" uniqueCount="43">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="2752" uniqueCount="43">
   <si>
     <t>Row</t>
   </si>
@@ -195,14 +195,14 @@
     <col min="3" max="3" width="11.42578125" customWidth="true"/>
     <col min="4" max="4" width="14.85546875" customWidth="true"/>
     <col min="5" max="5" width="12.85546875" customWidth="true"/>
-    <col min="6" max="6" width="11.140625" customWidth="true"/>
-    <col min="7" max="7" width="14.85546875" customWidth="true"/>
-    <col min="8" max="8" width="12.85546875" customWidth="true"/>
+    <col min="6" max="6" width="10.140625" customWidth="true"/>
+    <col min="7" max="7" width="15.85546875" customWidth="true"/>
+    <col min="8" max="8" width="15.85546875" customWidth="true"/>
     <col min="9" max="9" width="11.140625" customWidth="true"/>
-    <col min="10" max="10" width="11.140625" customWidth="true"/>
-    <col min="11" max="11" width="13.85546875" customWidth="true"/>
-    <col min="12" max="12" width="13.85546875" customWidth="true"/>
-    <col min="13" max="13" width="11.140625" customWidth="true"/>
+    <col min="10" max="10" width="15.85546875" customWidth="true"/>
+    <col min="11" max="11" width="15.85546875" customWidth="true"/>
+    <col min="12" max="12" width="15.85546875" customWidth="true"/>
+    <col min="13" max="13" width="15.85546875" customWidth="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -251,40 +251,40 @@
         <v>1</v>
       </c>
       <c r="B2" s="0">
-        <v>537369626</v>
+        <v>3715875</v>
       </c>
       <c r="C2" s="0">
-        <v>537391760</v>
+        <v>1568185</v>
       </c>
       <c r="D2" s="0">
-        <v>1074783520</v>
+        <v>3056392565</v>
       </c>
       <c r="E2" s="0">
-        <v>0</v>
+        <v>1112818631</v>
       </c>
       <c r="F2" s="0">
-        <v>1074522352</v>
+        <v>267904242</v>
       </c>
       <c r="G2" s="0">
-        <v>2147203448</v>
+        <v>132568197165</v>
       </c>
       <c r="H2" s="0">
-        <v>2146925120</v>
+        <v>313600074080</v>
       </c>
       <c r="I2" s="0">
-        <v>2678332088</v>
+        <v>3219168420</v>
       </c>
       <c r="J2" s="0">
-        <v>4294406896</v>
+        <v>6270940082160</v>
       </c>
       <c r="K2" s="0">
-        <v>5636252321</v>
+        <v>3993742239498</v>
       </c>
       <c r="L2" s="0">
-        <v>5636252321</v>
+        <v>4214817763749</v>
       </c>
       <c r="M2" s="0">
-        <v>6964681208</v>
+        <v>30139246532</v>
       </c>
     </row>
     <row r="3">
@@ -292,34 +292,34 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
-        <v>537391760</v>
+        <v>4100625</v>
       </c>
       <c r="C3" s="0">
-        <v>537286571</v>
+        <v>2451997</v>
       </c>
       <c r="D3" s="0">
-        <v>1074331184</v>
+        <v>3054824380</v>
       </c>
       <c r="E3" s="0">
-        <v>0</v>
+        <v>1534579128</v>
       </c>
       <c r="F3" s="0">
-        <v>1074493146</v>
+        <v>267453334</v>
       </c>
       <c r="G3" s="0">
-        <v>1074739252</v>
+        <v>313269867756</v>
       </c>
       <c r="H3" s="0">
-        <v>2148319959</v>
+        <v>313362817490</v>
       </c>
       <c r="I3" s="0">
-        <v>2675344297</v>
+        <v>2190475701</v>
       </c>
       <c r="J3" s="0">
-        <v>2147240664</v>
+        <v>3122071005375</v>
       </c>
       <c r="K3" s="0">
-        <v>4561310032</v>
+        <v>2633674724640</v>
       </c>
       <c r="L3" s="0">
         <v>0</v>
@@ -333,31 +333,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
-        <v>537369626</v>
+        <v>3683042</v>
       </c>
       <c r="C4" s="0">
-        <v>537268807</v>
+        <v>2395201</v>
       </c>
       <c r="D4" s="0">
-        <v>1074331184</v>
+        <v>1886526555</v>
       </c>
       <c r="E4" s="0">
-        <v>0</v>
+        <v>1803461736</v>
       </c>
       <c r="F4" s="0">
-        <v>1074378780</v>
+        <v>244075760</v>
       </c>
       <c r="G4" s="0">
-        <v>1612437132</v>
+        <v>475459580480</v>
       </c>
       <c r="H4" s="0">
-        <v>2146925120</v>
+        <v>521167824690</v>
       </c>
       <c r="I4" s="0">
-        <v>2147250176</v>
+        <v>3219168420</v>
       </c>
       <c r="J4" s="0">
-        <v>2147652520</v>
+        <v>2470998726750</v>
       </c>
       <c r="K4" s="0">
         <v>0</v>
@@ -374,31 +374,31 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>537171140</v>
+        <v>4102648</v>
       </c>
       <c r="C5" s="0">
-        <v>537357153</v>
+        <v>1458326</v>
       </c>
       <c r="D5" s="0">
-        <v>1073877548</v>
+        <v>2952204388</v>
       </c>
       <c r="E5" s="0">
-        <v>0</v>
+        <v>1534579128</v>
       </c>
       <c r="F5" s="0">
-        <v>1074522352</v>
+        <v>267904242</v>
       </c>
       <c r="G5" s="0">
-        <v>2148757560</v>
+        <v>505491842996</v>
       </c>
       <c r="H5" s="0">
-        <v>1610438580</v>
+        <v>522304705086</v>
       </c>
       <c r="I5" s="0">
-        <v>2679446389</v>
+        <v>2178471300</v>
       </c>
       <c r="J5" s="0">
-        <v>2686519876</v>
+        <v>2627236387800</v>
       </c>
       <c r="K5" s="0">
         <v>0</v>
@@ -415,31 +415,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>537369626</v>
+        <v>3683042</v>
       </c>
       <c r="C6" s="0">
-        <v>537391760</v>
+        <v>2451997</v>
       </c>
       <c r="D6" s="0">
-        <v>1074342280</v>
+        <v>4776490156</v>
       </c>
       <c r="E6" s="0">
-        <v>0</v>
+        <v>1803461736</v>
       </c>
       <c r="F6" s="0">
-        <v>1074493146</v>
+        <v>267904242</v>
       </c>
       <c r="G6" s="0">
-        <v>2147203448</v>
+        <v>284820120615</v>
       </c>
       <c r="H6" s="0">
-        <v>1342502669</v>
+        <v>311955682810</v>
       </c>
       <c r="I6" s="0">
-        <v>2679446389</v>
+        <v>2173007838</v>
       </c>
       <c r="J6" s="0">
-        <v>4297515120</v>
+        <v>4233019268424</v>
       </c>
       <c r="K6" s="0">
         <v>0</v>
@@ -456,25 +456,25 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>537171140</v>
+        <v>3714040</v>
       </c>
       <c r="C7" s="0">
-        <v>537391760</v>
+        <v>2395201</v>
       </c>
       <c r="D7" s="0">
-        <v>1074378780</v>
+        <v>2949752391</v>
       </c>
       <c r="E7" s="0">
-        <v>0</v>
+        <v>1803461736</v>
       </c>
       <c r="F7" s="0">
-        <v>1074436690</v>
+        <v>267453334</v>
       </c>
       <c r="G7" s="0">
-        <v>1074493146</v>
+        <v>322548720804</v>
       </c>
       <c r="H7" s="0">
-        <v>2147547786</v>
+        <v>314128690648</v>
       </c>
       <c r="I7" s="0">
         <v>0</v>
@@ -497,25 +497,25 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>537369626</v>
+        <v>3683042</v>
       </c>
       <c r="C8" s="0">
-        <v>537391760</v>
+        <v>2355872</v>
       </c>
       <c r="D8" s="0">
-        <v>1073877548</v>
+        <v>2883822004</v>
       </c>
       <c r="E8" s="0">
-        <v>0</v>
+        <v>3117495820</v>
       </c>
       <c r="F8" s="0">
-        <v>1074522352</v>
+        <v>259759426</v>
       </c>
       <c r="G8" s="0">
-        <v>2148684560</v>
+        <v>521877463416</v>
       </c>
       <c r="H8" s="0">
-        <v>1611003396</v>
+        <v>323241522795</v>
       </c>
       <c r="I8" s="0">
         <v>0</v>
@@ -538,25 +538,25 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>537189390</v>
+        <v>3714040</v>
       </c>
       <c r="C9" s="0">
-        <v>537286571</v>
+        <v>2451997</v>
       </c>
       <c r="D9" s="0">
-        <v>1074342280</v>
+        <v>4668246749</v>
       </c>
       <c r="E9" s="0">
-        <v>0</v>
+        <v>3088651544</v>
       </c>
       <c r="F9" s="0">
-        <v>1074436690</v>
+        <v>244075760</v>
       </c>
       <c r="G9" s="0">
-        <v>1610240992</v>
+        <v>521341654932</v>
       </c>
       <c r="H9" s="0">
-        <v>2147121040</v>
+        <v>321750847440</v>
       </c>
       <c r="I9" s="0">
         <v>0</v>
@@ -579,25 +579,25 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>537391760</v>
+        <v>4082408</v>
       </c>
       <c r="C10" s="0">
-        <v>537357153</v>
+        <v>2451997</v>
       </c>
       <c r="D10" s="0">
-        <v>1073371512</v>
+        <v>2881426803</v>
       </c>
       <c r="E10" s="0">
-        <v>0</v>
+        <v>3117495820</v>
       </c>
       <c r="F10" s="0">
-        <v>1074436690</v>
+        <v>259759426</v>
       </c>
       <c r="G10" s="0">
-        <v>1074187829</v>
+        <v>312490589478</v>
       </c>
       <c r="H10" s="0">
-        <v>2147164536</v>
+        <v>311955682810</v>
       </c>
       <c r="I10" s="0">
         <v>0</v>
@@ -620,25 +620,25 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>537171140</v>
+        <v>4108729</v>
       </c>
       <c r="C11" s="0">
-        <v>537357153</v>
+        <v>2395201</v>
       </c>
       <c r="D11" s="0">
-        <v>1073877548</v>
+        <v>2271488075</v>
       </c>
       <c r="E11" s="0">
-        <v>0</v>
+        <v>4799583164</v>
       </c>
       <c r="F11" s="0">
-        <v>1074436690</v>
+        <v>236758205</v>
       </c>
       <c r="G11" s="0">
-        <v>1074436690</v>
+        <v>202427566045</v>
       </c>
       <c r="H11" s="0">
-        <v>2147121040</v>
+        <v>314128690648</v>
       </c>
       <c r="I11" s="0">
         <v>0</v>
@@ -661,13 +661,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>537391760</v>
+        <v>4082408</v>
       </c>
       <c r="C12" s="0">
         <v>0</v>
       </c>
       <c r="D12" s="0">
-        <v>1074342280</v>
+        <v>2841392528</v>
       </c>
       <c r="E12" s="0">
         <v>0</v>
@@ -676,7 +676,7 @@
         <v>0</v>
       </c>
       <c r="G12" s="0">
-        <v>2148662368</v>
+        <v>475459580480</v>
       </c>
       <c r="H12" s="0">
         <v>0</v>
@@ -702,13 +702,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>537165592</v>
+        <v>3715875</v>
       </c>
       <c r="C13" s="0">
         <v>0</v>
       </c>
       <c r="D13" s="0">
-        <v>537206858</v>
+        <v>2841395700</v>
       </c>
       <c r="E13" s="0">
         <v>0</v>
@@ -717,7 +717,7 @@
         <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>2146743024</v>
+        <v>520464187964</v>
       </c>
       <c r="H13" s="0">
         <v>0</v>
@@ -743,13 +743,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>537391760</v>
+        <v>4082408</v>
       </c>
       <c r="C14" s="0">
         <v>0</v>
       </c>
       <c r="D14" s="0">
-        <v>1074378780</v>
+        <v>1172943144</v>
       </c>
       <c r="E14" s="0">
         <v>0</v>
@@ -758,7 +758,7 @@
         <v>0</v>
       </c>
       <c r="G14" s="0">
-        <v>1074071774</v>
+        <v>293623139280</v>
       </c>
       <c r="H14" s="0">
         <v>0</v>
@@ -784,13 +784,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>537189390</v>
+        <v>3715875</v>
       </c>
       <c r="C15" s="0">
         <v>0</v>
       </c>
       <c r="D15" s="0">
-        <v>1074378780</v>
+        <v>4776490156</v>
       </c>
       <c r="E15" s="0">
         <v>0</v>
@@ -799,7 +799,7 @@
         <v>0</v>
       </c>
       <c r="G15" s="0">
-        <v>1074436690</v>
+        <v>202427566045</v>
       </c>
       <c r="H15" s="0">
         <v>0</v>
@@ -825,13 +825,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>537171140</v>
+        <v>4084425</v>
       </c>
       <c r="C16" s="0">
         <v>0</v>
       </c>
       <c r="D16" s="0">
-        <v>1074378780</v>
+        <v>2949752391</v>
       </c>
       <c r="E16" s="0">
         <v>0</v>
@@ -840,7 +840,7 @@
         <v>0</v>
       </c>
       <c r="G16" s="0">
-        <v>1611842734</v>
+        <v>294355366560</v>
       </c>
       <c r="H16" s="0">
         <v>0</v>
@@ -866,13 +866,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>537189390</v>
+        <v>3681025</v>
       </c>
       <c r="C17" s="0">
         <v>0</v>
       </c>
       <c r="D17" s="0">
-        <v>537160395</v>
+        <v>1611783900</v>
       </c>
       <c r="E17" s="0">
         <v>0</v>
@@ -881,7 +881,7 @@
         <v>0</v>
       </c>
       <c r="G17" s="0">
-        <v>2148757560</v>
+        <v>521341654932</v>
       </c>
       <c r="H17" s="0">
         <v>0</v>
@@ -907,13 +907,13 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>537171140</v>
+        <v>4084425</v>
       </c>
       <c r="C18" s="0">
         <v>0</v>
       </c>
       <c r="D18" s="0">
-        <v>1074783520</v>
+        <v>4668246749</v>
       </c>
       <c r="E18" s="0">
         <v>0</v>
@@ -922,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="G18" s="0">
-        <v>2147164536</v>
+        <v>312490589478</v>
       </c>
       <c r="H18" s="0">
         <v>0</v>
@@ -948,13 +948,13 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
-        <v>537189390</v>
+        <v>3348875</v>
       </c>
       <c r="C19" s="0">
         <v>0</v>
       </c>
       <c r="D19" s="0">
-        <v>1073371512</v>
+        <v>2881426803</v>
       </c>
       <c r="E19" s="0">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="0">
-        <v>1074378780</v>
+        <v>172528114455</v>
       </c>
       <c r="H19" s="0">
         <v>0</v>
@@ -989,13 +989,13 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>537165592</v>
+        <v>3681025</v>
       </c>
       <c r="C20" s="0">
         <v>0</v>
       </c>
       <c r="D20" s="0">
-        <v>537357153</v>
+        <v>1908624564</v>
       </c>
       <c r="E20" s="0">
         <v>0</v>
@@ -1004,7 +1004,7 @@
         <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>1611842734</v>
+        <v>322548720804</v>
       </c>
       <c r="H20" s="0">
         <v>0</v>
@@ -1030,13 +1030,13 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>537189390</v>
+        <v>2919412</v>
       </c>
       <c r="C21" s="0">
         <v>0</v>
       </c>
       <c r="D21" s="0">
-        <v>1074783520</v>
+        <v>4593418050</v>
       </c>
       <c r="E21" s="0">
         <v>0</v>
@@ -1045,7 +1045,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="0">
-        <v>2148757560</v>
+        <v>521877463416</v>
       </c>
       <c r="H21" s="0">
         <v>0</v>
@@ -1077,7 +1077,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="0">
-        <v>1074331184</v>
+        <v>4591062451</v>
       </c>
       <c r="E22" s="0">
         <v>0</v>
@@ -1118,7 +1118,7 @@
         <v>0</v>
       </c>
       <c r="D23" s="0">
-        <v>1073582268</v>
+        <v>1611783900</v>
       </c>
       <c r="E23" s="0">
         <v>0</v>
@@ -1159,7 +1159,7 @@
         <v>0</v>
       </c>
       <c r="D24" s="0">
-        <v>1073582268</v>
+        <v>2952204388</v>
       </c>
       <c r="E24" s="0">
         <v>0</v>
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="D25" s="0">
-        <v>1074378780</v>
+        <v>2949752391</v>
       </c>
       <c r="E25" s="0">
         <v>0</v>
@@ -1241,7 +1241,7 @@
         <v>0</v>
       </c>
       <c r="D26" s="0">
-        <v>537525774</v>
+        <v>1908624564</v>
       </c>
       <c r="E26" s="0">
         <v>0</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="D27" s="0">
-        <v>537525774</v>
+        <v>2952204388</v>
       </c>
       <c r="E27" s="0">
         <v>0</v>
@@ -1323,7 +1323,7 @@
         <v>0</v>
       </c>
       <c r="D28" s="0">
-        <v>1074342280</v>
+        <v>4776490156</v>
       </c>
       <c r="E28" s="0">
         <v>0</v>
@@ -1364,7 +1364,7 @@
         <v>0</v>
       </c>
       <c r="D29" s="0">
-        <v>1073601724</v>
+        <v>1908624564</v>
       </c>
       <c r="E29" s="0">
         <v>0</v>
@@ -1405,7 +1405,7 @@
         <v>0</v>
       </c>
       <c r="D30" s="0">
-        <v>1073601724</v>
+        <v>2883822004</v>
       </c>
       <c r="E30" s="0">
         <v>0</v>
@@ -1446,7 +1446,7 @@
         <v>0</v>
       </c>
       <c r="D31" s="0">
-        <v>1073601724</v>
+        <v>4668246749</v>
       </c>
       <c r="E31" s="0">
         <v>0</v>
